--- a/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2015_2026/tabelas/causalidade_granger.xlsx
+++ b/output_tcc_var_selic_ativ_espec_Modelo8_subamostras/2015_2026/tabelas/causalidade_granger.xlsx
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4099374914505502</v>
+        <v>0.4099374914505536</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7459158206918961</v>
+        <v>0.7459158206918937</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -493,10 +493,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.38917055680019</v>
+        <v>0.3891705568001889</v>
       </c>
       <c r="E3" t="n">
-        <v>0.760843003232608</v>
+        <v>0.7608430032326087</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.5705236580205851</v>
+        <v>0.5705236580205778</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6345738705361846</v>
+        <v>0.6345738705361894</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.2503490510304447</v>
+        <v>0.2503490510304476</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8611020334267458</v>
+        <v>0.8611020334267439</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -573,14 +573,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.318913815434973</v>
+        <v>3.357757610951612</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07433370071235272</v>
+        <v>0.018540240598581</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -601,14 +601,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3.357757610951597</v>
+        <v>2.318913815434932</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01854024059858139</v>
+        <v>0.07433370071235677</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -633,10 +633,10 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.204962052119845</v>
+        <v>1.204962052119844</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3070757866461049</v>
+        <v>0.3070757866461051</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.178497407469949</v>
+        <v>1.178497407469929</v>
       </c>
       <c r="E9" t="n">
-        <v>0.317077181542976</v>
+        <v>0.3170771815429834</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -689,10 +689,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.3199303072930863</v>
+        <v>0.319930307293079</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8109728930954989</v>
+        <v>0.8109728930955042</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -717,10 +717,10 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.2479302118654026</v>
+        <v>0.247930211865401</v>
       </c>
       <c r="E11" t="n">
-        <v>0.862823756576381</v>
+        <v>0.8628237565763821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -741,14 +741,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.7007874448764945</v>
+        <v>0.9622765252000324</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5517982098529068</v>
+        <v>0.4100803455049323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -769,14 +769,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.962276525200029</v>
+        <v>0.7007874448765</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4100803455049336</v>
+        <v>0.551798209852903</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.28656819191506</v>
+        <v>0.2865681919150793</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8351170583354837</v>
+        <v>0.8351170583354697</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.5846317305400122</v>
+        <v>0.5846317305400117</v>
       </c>
       <c r="E15" t="n">
-        <v>0.625244274456549</v>
+        <v>0.6252442744565488</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.4484431302414955</v>
+        <v>0.4484431302415051</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7184835101634535</v>
+        <v>0.7184835101634466</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.3182880890040372</v>
+        <v>0.3182880890040413</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8121635952810276</v>
+        <v>0.8121635952810247</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -909,14 +909,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.294201396997047</v>
+        <v>3.477485187119877</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0767882773289779</v>
+        <v>0.01576389451198459</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -937,14 +937,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3.477485187119901</v>
+        <v>2.294201396997023</v>
       </c>
       <c r="E19" t="n">
-        <v>0.01576389451198408</v>
+        <v>0.07678827732898016</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1.159768348330789</v>
+        <v>1.159768348330775</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3243291577012655</v>
+        <v>0.3243291577012711</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -997,10 +997,10 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1.169053833379397</v>
+        <v>1.169053833379402</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3207155913065191</v>
+        <v>0.320715591306517</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1025,10 +1025,10 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.756768937744967</v>
+        <v>2.756768937744958</v>
       </c>
       <c r="E22" t="n">
-        <v>0.04160176799262567</v>
+        <v>0.04160176799262614</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.4871072462159114</v>
+        <v>0.4871072462159169</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6913470877476935</v>
+        <v>0.6913470877476896</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1077,14 +1077,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.588398122376863</v>
+        <v>0.7142908587618139</v>
       </c>
       <c r="E24" t="n">
-        <v>0.05205670875598743</v>
+        <v>0.5436678713828405</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1105,14 +1105,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.714290858761833</v>
+        <v>2.588398122376879</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5436678713828286</v>
+        <v>0.05205670875598634</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0.3195096710989906</v>
+        <v>0.3195096710989894</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8112778898430751</v>
+        <v>0.8112778898430761</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0.5287818725751291</v>
+        <v>0.5287818725751326</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6626538350070394</v>
+        <v>0.662653835007037</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>0.5691731350188448</v>
+        <v>0.5691731350188428</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6354713419719907</v>
+        <v>0.6354713419719921</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.2070920471143561</v>
+        <v>0.2070920471143568</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8915028617369355</v>
+        <v>0.8915028617369349</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1245,14 +1245,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2.002785330004003</v>
+        <v>4.006234517366886</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1123355590142847</v>
+        <v>0.007672409155149282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1273,14 +1273,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>4.006234517366912</v>
+        <v>2.002785330004013</v>
       </c>
       <c r="E31" t="n">
-        <v>0.007672409155149005</v>
+        <v>0.1123355590142832</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.394663061506182</v>
+        <v>1.39466306150617</v>
       </c>
       <c r="E32" t="n">
-        <v>0.2433092080923035</v>
+        <v>0.2433092080923071</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1333,10 +1333,10 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1.118053489987063</v>
+        <v>1.118053489987074</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3410107064557892</v>
+        <v>0.3410107064557847</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.7196779508639803</v>
+        <v>0.7196779508639843</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5404487390518606</v>
+        <v>0.540448739051858</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0.5249993309886708</v>
+        <v>0.5249993309886744</v>
       </c>
       <c r="E35" t="n">
-        <v>0.6652320896007797</v>
+        <v>0.6652320896007771</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1413,14 +1413,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1.127587827863377</v>
+        <v>0.9882662207045764</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3371327789044477</v>
+        <v>0.3977884124077633</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1441,14 +1441,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.9882662207045724</v>
+        <v>1.127587827863371</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3977884124077656</v>
+        <v>0.3371327789044505</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1473,10 +1473,10 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1.31432341508799</v>
+        <v>1.314323415087953</v>
       </c>
       <c r="E38" t="n">
-        <v>0.2686800210542042</v>
+        <v>0.2686800210542165</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>0.3827728558586976</v>
+        <v>0.3827728558586914</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7654563264201908</v>
+        <v>0.7654563264201952</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2.629241126444192</v>
+        <v>2.629241126444221</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0493064944888102</v>
+        <v>0.04930649448880831</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0.8236440040031462</v>
+        <v>0.8236440040031363</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4810806737128137</v>
+        <v>0.481080673712819</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1581,14 +1581,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3.001242015080526</v>
+        <v>5.421132449056423</v>
       </c>
       <c r="E42" t="n">
-        <v>0.02998627871227043</v>
+        <v>0.001095116538770386</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1609,14 +1609,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5.421132449056437</v>
+        <v>3.001242015080531</v>
       </c>
       <c r="E43" t="n">
-        <v>0.001095116538770365</v>
+        <v>0.02998627871227025</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2.998301185475512</v>
+        <v>2.998301185475514</v>
       </c>
       <c r="E44" t="n">
-        <v>0.08375981543218268</v>
+        <v>0.08375981543218257</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.5414389208446595</v>
+        <v>0.5414389208446555</v>
       </c>
       <c r="E45" t="n">
-        <v>0.4620652328387777</v>
+        <v>0.4620652328387794</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1697,10 +1697,10 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1.909254640214529</v>
+        <v>1.909254640214542</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1674542479466575</v>
+        <v>0.1674542479466562</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1725,10 +1725,10 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>0.4711055737326653</v>
+        <v>0.4711055737326682</v>
       </c>
       <c r="E47" t="n">
-        <v>0.4926894449025473</v>
+        <v>0.492689444902546</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1749,14 +1749,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DLN_Selic</t>
+          <t>DLN_Expectativa_Inflacao</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.0541955016137003</v>
+        <v>2.694426778916911</v>
       </c>
       <c r="E48" t="n">
-        <v>0.8159802885127113</v>
+        <v>0.1011156048137279</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1777,14 +1777,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DLN_Expectativa_Inflacao</t>
+          <t>DLN_Selic</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2.694426778916923</v>
+        <v>0.05419550161369738</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1011156048137272</v>
+        <v>0.8159802885127161</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
